--- a/leilaCards.xlsx
+++ b/leilaCards.xlsx
@@ -1429,12 +1429,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
+          <t>Permanent: Movement Speed +50</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
           <t>Kalıcı: Hareket hızı +50</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Hareket hızı artar</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
